--- a/reports/output_data.xlsx
+++ b/reports/output_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,15 +451,2459 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>44494.67184027778</v>
+        <v>43993.52708333333</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Фастфуд</t>
+          <t>Супермаркеты</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-130</v>
+        <v>-83.48</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>43993.5249537037</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-156.07</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>43992.50708333333</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-86.40000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>43991.75175925926</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>43991.64554398148</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-90.45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>43991.54494212963</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-49.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>43991.52962962963</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-115.69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>43990.87864583333</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-314.39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>43990.56083333334</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-87.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>43989.90971064815</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-49.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>43989.49773148148</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-99.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>43988.53976851852</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>43988.53461805556</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>43987.5896875</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-129.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>43987.58655092592</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>43986.52886574074</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-105.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>43986.52741898148</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-59.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>43986.521875</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>43985.80950231481</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-150.39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>43985.66842592593</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-283.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>43985.59648148148</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>43985.59486111111</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>43985.45125</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-53</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>43985.44649305556</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-102.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>43984.79045138889</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-420.77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>43984.49400462963</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>43984.49283564815</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-52.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>43983.57641203704</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>43983.5749074074</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>43981.59048611111</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-589.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>43981.55180555556</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>43981.54927083333</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-52.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>43980.79627314815</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-52.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>43980.79460648148</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-53</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>43979.82247685185</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-106.56</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>43979.50994212963</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-138</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>43979.50846064815</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-86.59999999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>43978.85828703704</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-44.9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>43978.46876157408</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>43978.4669212963</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-52.9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>43977.56190972222</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>43977.55800925926</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-86.59999999999999</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43976.730625</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-238.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>43976.45150462963</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-52.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>43976.39634259259</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-53</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>43975.41795138889</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-135</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>43974.66496527778</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>43973.80642361111</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-134.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>43973.68143518519</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-383.41</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>43972.65274305556</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-103.39</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>43971.59207175926</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-135</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>43971.59016203704</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-114.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>43971.47677083333</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-52.9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>43970.43354166667</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-131.18</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>43969.87638888889</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>43969.66449074074</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>-295.7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>43969.50856481482</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>-59.6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>43968.58336805556</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>-135</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>43967.63265046296</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>-26.64</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>43967.62810185185</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-106.56</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>43967.56112268518</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>43966.6153587963</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>-184.73</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>43966.61216435185</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>-115.6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>43965.65576388889</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>43964.60481481482</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-135</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>43963.73005787037</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>-53</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>43962.82736111111</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>-183.6</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>43962.63328703704</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-135</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>43961.67070601852</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>-53</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>43960.69785879629</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>43960.69637731482</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>-114.84</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>43960.69483796296</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>43960.48371527778</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>-156.38</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>43958.74119212963</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>-160.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>43958.55813657407</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>-63.9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>43956.9287962963</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>-426.6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>43956.91179398148</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>-167.31</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>43956.66601851852</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>-154.8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>43956.66414351852</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>43955.73795138889</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>-297.48</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>43954.62262731481</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>-132.7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>43954.61677083333</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>-107.96</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>43954.60952546296</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>-165.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>43953.65203703703</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>-35.95</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>43952.68085648148</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>-107.61</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>43952.61615740741</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>-157.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>43951.72413194444</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>-67.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>43951.67421296296</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>-164.73</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>43950.6530324074</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>-157.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>43948.56993055555</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>-157.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>43948.56209490741</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>-131.04</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>43947.62678240741</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>43947.62570601852</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>-75.90000000000001</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>43947.62215277777</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>-66.38</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>43946.6196875</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>-118.98</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>43946.60579861111</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>-135.24</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>43945.65733796296</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>-107.45</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>43945.65621527778</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>-41.9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>43945.6396875</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>-220</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>43944.4984375</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-44.4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>43942.8940625</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>-105.8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>43942.55145833334</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>-89.78</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>43942.44386574074</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>-75.59999999999999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>43940.50809027778</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>-39.8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>43939.59902777777</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>-709.8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>43937.63390046296</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>-97.06</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>43937.63277777778</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>43936.73648148148</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>-134</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>43936.72400462963</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>43935.89855324074</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>-160.8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>43935.69893518519</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>43935.55957175926</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>-53.9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>43935.49136574074</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>-45.6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>43934.85137731482</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>-147.99</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>43934.65983796296</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>-88.65000000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>43933.58673611111</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>-174.8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>43932.81466435185</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>-175.08</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>43932.70135416667</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>-151.65</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>43932.69916666667</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>43931.60981481482</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>-67.73</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>43930.64042824074</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>-155.45</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>43930.62539351852</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>-266.32</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>43929.54188657407</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>-175.49</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>43929.52582175926</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>-68.63</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>43928.80579861111</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>-195.3</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>43928.69805555556</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>-233.8</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>43928.69508101852</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>-68.18000000000001</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>43928.51452546296</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>43927.66082175926</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>-159.75</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>43926.69277777777</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>-66.83</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>43925.89100694445</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>-116</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>43925.87898148148</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>-200.46</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>43925.7300462963</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>-67.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>43925.71802083333</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>43925.71357638889</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>-132.7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>43924.65375</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>-108.67</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>43924.56282407408</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>-157.5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>43923.85501157407</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>-278.22</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>43923.54752314815</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>-105.8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>43922.73313657408</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>-220.8</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>43922.72552083333</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>43922.60671296297</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>-67.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>43921.53832175926</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>-157.5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>43920.82118055555</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>-25.9</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>43920.56261574074</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>-192.43</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>43920.56068287037</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>-283.6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>43919.93613425926</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>-107.8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>43919.62174768518</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>-234.09</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>43918.61431712963</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>-99.2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>43918.60445601852</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>-150.08</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>43917.80469907408</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>-194.3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>43917.67303240741</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>-116.5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>43917.53267361111</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>43917.52334490741</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>-128.69</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>43917.52016203704</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>-66.05</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>43916.66251157408</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>-67.73</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>43916.56361111111</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>-93.15000000000001</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>43915.68547453704</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>-104.48</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>43915.58550925926</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>-82.13</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>43915.58365740741</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>43914.5283912037</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>-227.7</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>43913.6649537037</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>-103.82</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>43913.58618055555</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>-67.95</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>43912.86034722222</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>-177.8</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>43912.6043287037</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>43912.59680555556</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>-256.3</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>43911.60563657407</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>-68.04000000000001</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>43911.52428240741</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>-241.5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>43910.76027777778</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>-107.7</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>43910.65689814815</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>-103.53</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>43910.47099537037</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>-157.5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>43909.75663194444</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>-177.5</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>43909.51339120371</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>43908.85348379629</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>-109</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>43908.84770833333</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>-95.47</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>43908.71200231482</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>43908.4715162037</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>-25.14</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>43908.46835648148</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>-67.5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>43907.63305555555</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>43907.60965277778</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>43907.60712962963</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>-219.7</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>43906.75793981482</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>43906.60137731482</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>43906.53875</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>-67.5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>43905.75306712963</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>-449.9</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>43905.44863425926</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>-49.24</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>43904.68230324074</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>-508.87</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>43904.59722222222</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>-151.88</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>43904.59480324074</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Супермаркеты</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>-39.9</v>
       </c>
     </row>
   </sheetData>
